--- a/core/tests/testcases/basics/01_1nurse_1shift_12day_fix_shift_count_penalty_ortools_9.12_bug.prettify.xlsx
+++ b/core/tests/testcases/basics/01_1nurse_1shift_12day_fix_shift_count_penalty_ortools_9.12_bug.prettify.xlsx
@@ -26,20 +26,15 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DBEAFE"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="6">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -65,24 +60,11 @@
         <color rgb="00374151"/>
       </bottom>
     </border>
-    <border>
-      <right style="medium">
-        <color rgb="009CA3AF"/>
-      </right>
-    </border>
-    <border>
-      <right style="medium">
-        <color rgb="009CA3AF"/>
-      </right>
-      <bottom style="medium">
-        <color rgb="00374151"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -90,22 +72,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -481,10 +451,10 @@
       <c r="B1" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="C1" s="3" t="n">
+      <c r="C1" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="D1" s="4" t="n">
+      <c r="D1" s="2" t="n">
         <v>20</v>
       </c>
       <c r="E1" s="2" t="n">
@@ -502,10 +472,10 @@
       <c r="I1" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="J1" s="3" t="n">
+      <c r="J1" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="K1" s="4" t="n">
+      <c r="K1" s="2" t="n">
         <v>27</v>
       </c>
       <c r="L1" s="2" t="n">
@@ -529,190 +499,190 @@
       <c r="V1" s="2" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr"/>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr"/>
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Sat</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>Sun</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Mon</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>Tue</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Wed</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="I2" s="6" t="inlineStr">
+      <c r="I2" s="4" t="inlineStr">
         <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="J2" s="7" t="inlineStr">
+      <c r="J2" s="4" t="inlineStr">
         <is>
           <t>Sat</t>
         </is>
       </c>
-      <c r="K2" s="8" t="inlineStr">
+      <c r="K2" s="4" t="inlineStr">
         <is>
           <t>Sun</t>
         </is>
       </c>
-      <c r="L2" s="6" t="inlineStr">
+      <c r="L2" s="4" t="inlineStr">
         <is>
           <t>Mon</t>
         </is>
       </c>
-      <c r="M2" s="6" t="inlineStr">
+      <c r="M2" s="4" t="inlineStr">
         <is>
           <t>Tue</t>
         </is>
       </c>
-      <c r="N2" s="6" t="inlineStr">
+      <c r="N2" s="4" t="inlineStr">
         <is>
           <t>Wed</t>
         </is>
       </c>
-      <c r="O2" s="5" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="P2" s="6" t="inlineStr"/>
-      <c r="Q2" s="5" t="inlineStr">
+      <c r="P2" s="4" t="inlineStr"/>
+      <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>OFF (Total)</t>
         </is>
       </c>
-      <c r="R2" s="6" t="inlineStr">
+      <c r="R2" s="4" t="inlineStr">
         <is>
           <t>OFF (Weekday)</t>
         </is>
       </c>
-      <c r="S2" s="5" t="inlineStr">
+      <c r="S2" s="3" t="inlineStr">
         <is>
           <t>OFF (Weekend)</t>
         </is>
       </c>
-      <c r="T2" s="5" t="inlineStr">
+      <c r="T2" s="3" t="inlineStr">
         <is>
           <t>D Count</t>
         </is>
       </c>
-      <c r="U2" s="6" t="inlineStr"/>
-      <c r="V2" s="6" t="inlineStr"/>
+      <c r="U2" s="4" t="inlineStr"/>
+      <c r="V2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C3" s="7" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G3" s="6" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="H3" s="6" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="J3" s="7" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="K3" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="L3" s="6" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="M3" s="6" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="N3" s="6" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="O3" s="5" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P3" s="6" t="inlineStr"/>
-      <c r="Q3" s="5" t="n">
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr"/>
+      <c r="Q3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="R3" s="6" t="n">
+      <c r="R3" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="S3" s="5" t="n">
+      <c r="S3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="T3" s="5" t="n">
+      <c r="T3" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="U3" s="6" t="inlineStr"/>
-      <c r="V3" s="6" t="inlineStr"/>
+      <c r="U3" s="4" t="inlineStr"/>
+      <c r="V3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -723,15 +693,15 @@
       <c r="B4" s="2" t="n">
         <v>-10000</v>
       </c>
-      <c r="C4" s="3" t="inlineStr"/>
-      <c r="D4" s="4" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="3" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr"/>
@@ -745,49 +715,49 @@
       <c r="V4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>OPTIMAL</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr"/>
-      <c r="D5" s="8" t="inlineStr"/>
-      <c r="E5" s="6" t="inlineStr"/>
-      <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr"/>
-      <c r="H5" s="6" t="inlineStr"/>
-      <c r="I5" s="6" t="inlineStr"/>
-      <c r="J5" s="7" t="inlineStr"/>
-      <c r="K5" s="8" t="inlineStr"/>
-      <c r="L5" s="6" t="inlineStr"/>
-      <c r="M5" s="6" t="inlineStr"/>
-      <c r="N5" s="6" t="inlineStr"/>
-      <c r="O5" s="5" t="inlineStr"/>
-      <c r="P5" s="6" t="inlineStr"/>
-      <c r="Q5" s="5" t="inlineStr"/>
-      <c r="R5" s="6" t="inlineStr"/>
-      <c r="S5" s="5" t="inlineStr"/>
-      <c r="T5" s="5" t="inlineStr"/>
-      <c r="U5" s="6" t="inlineStr"/>
-      <c r="V5" s="6" t="inlineStr"/>
+      <c r="C5" s="4" t="inlineStr"/>
+      <c r="D5" s="4" t="inlineStr"/>
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr"/>
+      <c r="J5" s="4" t="inlineStr"/>
+      <c r="K5" s="4" t="inlineStr"/>
+      <c r="L5" s="4" t="inlineStr"/>
+      <c r="M5" s="4" t="inlineStr"/>
+      <c r="N5" s="4" t="inlineStr"/>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="4" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="4" t="inlineStr"/>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="4" t="inlineStr"/>
+      <c r="V5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr"/>
-      <c r="C6" s="3" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="3" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr"/>
@@ -801,60 +771,60 @@
       <c r="V6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>D Count</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="P7" s="6" t="inlineStr"/>
-      <c r="Q7" s="5" t="inlineStr"/>
-      <c r="R7" s="6" t="inlineStr"/>
-      <c r="S7" s="5" t="inlineStr"/>
-      <c r="T7" s="5" t="inlineStr"/>
-      <c r="U7" s="6" t="inlineStr"/>
-      <c r="V7" s="6" t="inlineStr"/>
+      <c r="B7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" s="4" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="4" t="inlineStr"/>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="4" t="inlineStr"/>
+      <c r="V7" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/core/tests/testcases/basics/01_1nurse_1shift_12day_fix_shift_count_penalty_ortools_9.12_bug.prettify.xlsx
+++ b/core/tests/testcases/basics/01_1nurse_1shift_12day_fix_shift_count_penalty_ortools_9.12_bug.prettify.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V7"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,13 +490,6 @@
       <c r="O1" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="P1" s="2" t="inlineStr"/>
-      <c r="Q1" s="1" t="inlineStr"/>
-      <c r="R1" s="2" t="inlineStr"/>
-      <c r="S1" s="1" t="inlineStr"/>
-      <c r="T1" s="1" t="inlineStr"/>
-      <c r="U1" s="2" t="inlineStr"/>
-      <c r="V1" s="2" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr"/>
@@ -570,29 +563,6 @@
           <t>Thu</t>
         </is>
       </c>
-      <c r="P2" s="4" t="inlineStr"/>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>OFF (Total)</t>
-        </is>
-      </c>
-      <c r="R2" s="4" t="inlineStr">
-        <is>
-          <t>OFF (Weekday)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>OFF (Weekend)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>D Count</t>
-        </is>
-      </c>
-      <c r="U2" s="4" t="inlineStr"/>
-      <c r="V2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
@@ -668,21 +638,6 @@
           <t>D</t>
         </is>
       </c>
-      <c r="P3" s="4" t="inlineStr"/>
-      <c r="Q3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="U3" s="4" t="inlineStr"/>
-      <c r="V3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -706,13 +661,6 @@
       <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="1" t="inlineStr"/>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="1" t="inlineStr"/>
-      <c r="R4" s="2" t="inlineStr"/>
-      <c r="S4" s="1" t="inlineStr"/>
-      <c r="T4" s="1" t="inlineStr"/>
-      <c r="U4" s="2" t="inlineStr"/>
-      <c r="V4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -738,13 +686,6 @@
       <c r="M5" s="4" t="inlineStr"/>
       <c r="N5" s="4" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr"/>
-      <c r="P5" s="4" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="4" t="inlineStr"/>
-      <c r="S5" s="3" t="inlineStr"/>
-      <c r="T5" s="3" t="inlineStr"/>
-      <c r="U5" s="4" t="inlineStr"/>
-      <c r="V5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr"/>
@@ -762,13 +703,6 @@
       <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="1" t="inlineStr"/>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="1" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
-      <c r="S6" s="1" t="inlineStr"/>
-      <c r="T6" s="1" t="inlineStr"/>
-      <c r="U6" s="2" t="inlineStr"/>
-      <c r="V6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -818,13 +752,6 @@
       <c r="O7" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="P7" s="4" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="4" t="inlineStr"/>
-      <c r="S7" s="3" t="inlineStr"/>
-      <c r="T7" s="3" t="inlineStr"/>
-      <c r="U7" s="4" t="inlineStr"/>
-      <c r="V7" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/core/tests/testcases/basics/01_1nurse_1shift_12day_fix_shift_count_penalty_ortools_9.12_bug.prettify.xlsx
+++ b/core/tests/testcases/basics/01_1nurse_1shift_12day_fix_shift_count_penalty_ortools_9.12_bug.prettify.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -687,72 +687,6 @@
       <c r="N5" s="4" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr"/>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr"/>
-      <c r="B6" s="2" t="inlineStr"/>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr"/>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr"/>
-      <c r="O6" s="1" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>D Count</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
